--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.5.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y244"/>
+  <dimension ref="A1:Y274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>L446: possible duplicated/overlap line with previous line (similarity 63%) :: South Brant ï¼› Mr. Balfour over 800 in</t>
+          <t>L446: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | possible duplicated/overlap line with previous line (similarity 64%) :: South Brant ； Mr. Balfour over 800 in</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L241: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: COâ€™S.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L95: isolated marker/symbol line :: 6</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>803</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -715,17 +719,17 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c eachâ€”Perfect Goods.</t>
+          <t>L50: suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c each—Perfect Goods.</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L245: stray/suspicious non-ASCII glyph(s): U+FF06 FULLWIDTH AMPERSAND | isolated marker/symbol line :: ＆</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 10c (letter/digit mix) :: A Large Line of Ribbed Cotton Vests, Shaped and Straight, Only 10c eachâ€”Perfect Goods.</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -807,12 +811,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
+          <t>L446: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | possible duplicated/overlap line with previous line (similarity 64%) :: South Brant ； Mr. Balfour over 800 in</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: alive and thatâ€™s all; Mr. Goold, a black-</t>
+          <t>L1062: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -834,13 +838,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
+          <t>L248: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: ------— **** -----</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
+          <t>L267: line starts with punctuation glued to text :: ** No person accepting or holding any</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -858,12 +862,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>322</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>131</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -882,14 +886,10 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L162: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Algomaâ€”Some</t>
-        </is>
-      </c>
+          <t>L450: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: in East Huron ； Mr. Ferguson 600</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -909,13 +909,13 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ****-----------</t>
+          <t>L252: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — ****-----------</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L267: line starts with punctuation glued to text :: ** No person accepting or holding any</t>
+          <t>L416: line starts with punctuation glued to text :: ** If any person hereby disqualified or</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -957,14 +957,10 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Hartley in a Most Revolting Lightâ€”The</t>
-        </is>
-      </c>
+          <t>L572: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -988,11 +984,7 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>L416: line starts with punctuation glued to text :: ** If any person hereby disqualified or</t>
-        </is>
-      </c>
+      <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1032,14 +1024,10 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Attorney-Generalâ€™s Department, decided</t>
-        </is>
-      </c>
+          <t>L611: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1103,14 +1091,10 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: house is my own and I donâ€™t care";</t>
-        </is>
-      </c>
+          <t>L612: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1120,7 +1104,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L290: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1..........</t>
+          <t>L248: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: ------— **** -----</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1174,14 +1158,10 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: wouldnâ€™t, and did not for about four</t>
-        </is>
-      </c>
+          <t>L625: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Blouses, nicely made, with sailor collar ； different patterns, all sizes. We will sell this lot at</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1191,7 +1171,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L292: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...........</t>
+          <t>L252: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: — ****-----------</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1221,12 +1201,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1245,14 +1225,10 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ------â€” **** -----</t>
-        </is>
-      </c>
+          <t>L629: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1262,7 +1238,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L294: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
+          <t>L290: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1..........</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1297,7 +1273,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1311,19 +1287,15 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-â€”</t>
+          <t>L331: suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-—</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ****-----------</t>
-        </is>
-      </c>
+          <t>L638: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1333,7 +1305,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L296: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
+          <t>L292: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...........</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1363,12 +1335,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>273</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1387,24 +1359,20 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: ... â€¢â€¢â€¢</t>
-        </is>
-      </c>
+          <t>L642: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L156: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L298: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 6..........</t>
+          <t>L294: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1453,29 +1421,25 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) :: â€”____________________=85c. â€” â€”________________</t>
+          <t>L477: suspicious token(s): 85c (letter/digit mix) :: —____________________=85c. — —________________</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L188: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L331: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 0O (letter/digit mix) :: ======$2.0O-â€”</t>
-        </is>
-      </c>
+          <t>L777: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L157: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L300: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 7 ... ... ...</t>
+          <t>L296: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1485,7 +1449,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: ... â€¢â€¢â€¢</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1510,7 +1474,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1529,29 +1493,25 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L425: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 876 fringed in Haldimand, and Mr. Sennâ€™s</t>
-        </is>
-      </c>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): 6OO (letter/digit mix) :: Prescott； Mr. Robillard nearly 6OO in Rus-</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 46</t>
+          <t>L158: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L302: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 8..........</t>
+          <t>L298: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 6..........</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h-- of a note or a d â€”â€” of</t>
+          <t>L732: punctuation artifact: double/multiple hyphen :: said it's a h-- of a note or a d —— of</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -1600,24 +1560,20 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nipissing ; Mr. Bronson and Mr. Oâ€™Keefe</t>
-        </is>
-      </c>
+          <t>L858: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: 50</t>
+          <t>L159: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L305: isolated marker/symbol line :: 50</t>
+          <t>L300: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 7 ... ... ...</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -1671,24 +1627,20 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L197: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 85c (letter/digit mix) :: â€”____________________=85c. â€” â€”________________</t>
-        </is>
-      </c>
+          <t>L866: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 27;Liberal Patrons,7;；</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L161: isolated marker/symbol line :: 2</t>
+          <t>L160: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L307: isolated marker/symbol line :: 54</t>
+          <t>L302: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 8..........</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -1742,24 +1694,20 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: canvassersâ€™ reports when men vote under</t>
-        </is>
-      </c>
+          <t>L923: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L162: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L161: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L308: isolated marker/symbol line :: 46</t>
+          <t>L305: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -1801,24 +1749,20 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: most of Adamâ€™sdescendants, they base</t>
-        </is>
-      </c>
+          <t>L957: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L163: isolated marker/symbol line :: .</t>
+          <t>L162: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L309: symbol-only separator/garbage line :: . 67</t>
+          <t>L307: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1856,24 +1800,20 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: she said if I wouldnâ€™t she would have</t>
-        </is>
-      </c>
+          <t>L1022: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L164: isolated marker/symbol line :: 0</t>
+          <t>L163: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L310: symbol-only separator/garbage line :: .125</t>
+          <t>L308: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1909,26 +1849,18 @@
           <t>L669: suspicious token(s): 123c (letter/digit mix) :: ful goods, 10 and 123c each, extra quality at 15</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to Quiggâ€™s, and the boys got beer and</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L165: isolated marker/symbol line :: .</t>
+          <t>L164: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L311: symbol-only separator/garbage line :: .123</t>
+          <t>L309: symbol-only separator/garbage line :: . 67</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1961,29 +1893,21 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladiesâ€™ Balbriggan Vests. Men 8</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L211: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L617: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: can take it out inâ€™that way"; it was</t>
-        </is>
-      </c>
+          <t>L670: suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladies’ Balbriggan Vests. Men 8</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L166: isolated marker/symbol line :: .</t>
+          <t>L165: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L312: symbol-only separator/garbage line :: .80</t>
+          <t>L310: symbol-only separator/garbage line :: .125</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -2019,26 +1943,18 @@
           <t>L678: suspicious token(s): Stripe1Bathing (letter/digit mix) :: selling off at big reductions. Stripe1Bathing</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: each. Finch Bros.â€™ is the house for these goods.</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L166: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L313: symbol-only separator/garbage line :: .90</t>
+          <t>L311: symbol-only separator/garbage line :: .123</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -2074,26 +1990,18 @@
           <t>L679: suspicious token(s): 39c (letter/digit mix), 65c (letter/digit mix) :: Flannels 39c, worth 65c. Plain French Twill</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L213: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L660: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: seasonâ€™s, but we have made deep cuts in the</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L171: isolated marker/symbol line :: 67</t>
+          <t>L167: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L314: symbol-only separator/garbage line :: .40</t>
+          <t>L312: symbol-only separator/garbage line :: .80</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -2129,26 +2037,18 @@
           <t>L680: suspicious token(s): 25c (letter/digit mix), 40c (letter/digit mix) :: Bathing Flannel 25c, worth 40c. Childrens</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L219: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 20c (letter/digit mix) :: and 20c each. Ladiesâ€™ Balbriggan Vests. Men 8</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L172: isolated marker/symbol line :: 44</t>
+          <t>L168: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L318: isolated marker/symbol line :: 44</t>
+          <t>L313: symbol-only separator/garbage line :: .90</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2181,29 +2081,21 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blousesâ€”40c, for 29c; 50c, for 39c; 75c,</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L233: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Drawers. Ladiesâ€™ and Men's Hostery. Child-</t>
-        </is>
-      </c>
+          <t>L684: suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blouses—40c, for 29c; 50c, for 39c; 75c,</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L173: isolated marker/symbol line :: 8</t>
+          <t>L169: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: 77</t>
+          <t>L314: symbol-only separator/garbage line :: .40</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2239,26 +2131,18 @@
           <t>L685: suspicious token(s): 50c (letter/digit mix), 40c (letter/digit mix), 25c (letter/digit mix), 50c (letter/digit mix) :: for 50c. White Lawn Blouses 40c, for 25c. 50c</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 40c (letter/digit mix), 29c (letter/digit mix), 50c (letter/digit mix), 39c (letter/digit mix), 75c (letter/digit mix) :: Print Blousesâ€”40c, for 29c; 50c, for 39c; 75c,</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L175: isolated marker/symbol line :: .</t>
+          <t>L170: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L322: isolated marker/symbol line :: 13</t>
+          <t>L316: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... •••</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2286,7 +2170,7 @@
       <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>L848: suspicious token(s): 6OO (letter/digit mix) :: Prescottï¼› Mr. Robillard nearly 6OO in Rus-</t>
+          <t>L848: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): 6OO (letter/digit mix) :: Prescott； Mr. Robillard nearly 6OO in Rus-</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
@@ -2294,26 +2178,18 @@
           <t>L686: suspicious token(s): 39c (letter/digit mix), 65c (letter/digit mix), 49c (letter/digit mix), 70c (letter/digit mix), 59c (letter/digit mix) :: - Blouses 39c. 65c Blouses 49c. 70c Blouses 59c.</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L751: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at the house at 4 oâ€™clock ; when I got</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L171: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L324: isolated marker/symbol line :: 41</t>
+          <t>L318: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2349,26 +2225,18 @@
           <t>L703: suspicious token(s): 25c (letter/digit mix), 22c (letter/digit mix) :: extra large, 3 for 25c and 2 for 22c. Beach</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L241: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a dâ€” of</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L177: isolated marker/symbol line :: .</t>
+          <t>L172: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: 16</t>
+          <t>L320: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2404,26 +2272,18 @@
           <t>L736: suspicious token(s): 25c (letter/digit mix) :: Fine Dress Sateens 20 and 25c, nowselling off</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L810: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BERTRAMâ€™S</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L173: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L327: symbol-only separator/garbage line :: 21%</t>
+          <t>L322: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2459,26 +2319,18 @@
           <t>L738: suspicious token(s): 15c (letter/digit mix) :: 15c. all new styles. Handsome Broche Sateens</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: toriousâ€”being mistaken or classed together</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: .</t>
+          <t>L174: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L329: symbol-only separator/garbage line :: 631 284</t>
+          <t>L324: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2511,29 +2363,21 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 33Women (letter/digit mix) :: Our $1.33Womenâ€™s Strapor Tie Slippers we can</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L473: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L824: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: with _. but weâ€™ve said enough on this subject</t>
-        </is>
-      </c>
+          <t>L839: suspicious token(s): 33Women’s (letter/digit mix) :: Our $1.33Women’s Strapor Tie Slippers we can</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L180: isolated marker/symbol line :: 125</t>
+          <t>L175: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L339: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
+          <t>L326: isolated marker/symbol line :: 16</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2569,26 +2413,18 @@
           <t>L847: suspicious token(s): Our32 (letter/digit mix) :: Our32.25 Men's Laced or Congress Boots we</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 33Women (letter/digit mix) :: Our $1.33Womenâ€™s Strapor Tie Slippers we can</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: 77</t>
+          <t>L176: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L341: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2..........</t>
+          <t>L327: symbol-only separator/garbage line :: 21%</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2620,26 +2456,18 @@
           <t>L946: punctuation artifact: repeated exclamation marks | suspicious token(s): PUI0 (letter/digit mix) :: KIIW an Ma PUI0 ua!!!!setive A . aO</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our $1.35 Womenâ€™s Dongola Oxford Tie Shoes</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L182: isolated marker/symbol line :: 4</t>
+          <t>L177: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L343: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3..........</t>
+          <t>L329: symbol-only separator/garbage line :: 631 284</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2667,26 +2495,18 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our 83 75 Menâ€™s Shell Cordovan Congress and</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L183: isolated marker/symbol line :: .</t>
+          <t>L178: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L345: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
+          <t>L339: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2714,26 +2534,18 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L850: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Our $1.75 Menâ€™s Laced Boots wo can prove to</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L184: isolated marker/symbol line :: .</t>
+          <t>L179: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L347: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
+          <t>L341: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2..........</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2761,26 +2573,18 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L495: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: in Fred coming home, he couldnâ€™t do</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L185: isolated marker/symbol line :: .</t>
+          <t>L180: isolated marker/symbol line :: 125</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L349: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 63........</t>
+          <t>L343: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3..........</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2808,26 +2612,18 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L997: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Branch Office, 31 King west, â€˜Phone 978</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L186: isolated marker/symbol line :: Â·</t>
+          <t>L181: isolated marker/symbol line :: 77</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: 57</t>
+          <t>L345: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4..........</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2855,26 +2651,18 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L497: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L1054: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and gentsâ€™, smoking</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L187: isolated marker/symbol line :: .</t>
+          <t>L182: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L353: isolated marker/symbol line :: 29</t>
+          <t>L347: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5..........</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2902,26 +2690,18 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L1060: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ADVERTISE IN THE TIMESâ€”</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L188: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L183: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L355: isolated marker/symbol line :: 12</t>
+          <t>L349: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 63........</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2949,26 +2729,18 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L1062: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢*</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L189: isolated marker/symbol line :: .</t>
+          <t>L184: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L357: isolated marker/symbol line :: 46</t>
+          <t>L351: isolated marker/symbol line :: 57</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2996,22 +2768,18 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L185: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L359: isolated marker/symbol line :: 47</t>
+          <t>L353: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -3039,28 +2807,24 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L186: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L361: isolated marker/symbol line :: 51</t>
+          <t>L355: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L763: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a dâ€” of</t>
+          <t>L763: punctuation artifact: double/multiple hyphen :: said it's a h---of a note or a d— of</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -3082,22 +2846,18 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L504: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L192: isolated marker/symbol line :: .</t>
+          <t>L187: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 242</t>
+          <t>L357: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -3125,22 +2885,18 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L193: isolated marker/symbol line :: 13</t>
+          <t>L188: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L365: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 43</t>
+          <t>L359: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3164,22 +2920,18 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L194: isolated marker/symbol line :: 123</t>
+          <t>L189: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L367: symbol-only separator/garbage line :: .....30</t>
+          <t>L361: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3203,22 +2955,18 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L195: isolated marker/symbol line :: 456</t>
+          <t>L190: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L369: symbol-only separator/garbage line :: .....46</t>
+          <t>L363: isolated marker/symbol line :: 242</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3242,22 +2990,18 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L515: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L196: isolated marker/symbol line :: D</t>
+          <t>L191: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L371: symbol-only separator/garbage line :: .....56</t>
+          <t>L365: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 43</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -3281,22 +3025,18 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L516: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L197: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L192: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L373: symbol-only separator/garbage line :: .....34</t>
+          <t>L367: symbol-only separator/garbage line :: .....30</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -3320,22 +3060,18 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L517: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L199: isolated marker/symbol line :: .</t>
+          <t>L193: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L375: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 35.</t>
+          <t>L369: symbol-only separator/garbage line :: .....46</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3359,22 +3095,18 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦.</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L200: isolated marker/symbol line :: .</t>
+          <t>L194: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L377: isolated marker/symbol line :: 250</t>
+          <t>L371: symbol-only separator/garbage line :: .....56</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -3398,22 +3130,18 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L195: isolated marker/symbol line :: 456</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: $1.75</t>
+          <t>L373: symbol-only separator/garbage line :: .....34</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3437,22 +3165,18 @@
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L196: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L389: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... *** ***</t>
+          <t>L375: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... ... 35.</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3476,22 +3200,18 @@
       <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L527: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L203: isolated marker/symbol line :: .</t>
+          <t>L197: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L391: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ......</t>
+          <t>L377: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3515,22 +3235,18 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L198: isolated marker/symbol line :: .·.</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L393: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ................</t>
+          <t>L385: symbol-only separator/garbage line :: $1.75</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
@@ -3554,22 +3270,18 @@
       <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L531: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L206: isolated marker/symbol line :: .</t>
+          <t>L199: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: 67</t>
+          <t>L389: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... *** ***</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3593,22 +3305,18 @@
       <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L532: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L207: isolated marker/symbol line :: 80</t>
+          <t>L200: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: 78</t>
+          <t>L391: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ......</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3632,22 +3340,18 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L208: isolated marker/symbol line :: 41</t>
+          <t>L201: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L399: isolated marker/symbol line :: 54</t>
+          <t>L393: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ................</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3671,22 +3375,18 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L209: isolated marker/symbol line :: 6</t>
+          <t>L202: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: 199</t>
+          <t>L395: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3710,22 +3410,18 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L548: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: .â€¦</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L210: isolated marker/symbol line :: .</t>
+          <t>L203: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L406: isolated marker/symbol line :: a</t>
+          <t>L397: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3749,22 +3445,18 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L550: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L204: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L407: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 63</t>
+          <t>L399: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3788,22 +3480,18 @@
       <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L551: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L213: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L205: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L408: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L405: isolated marker/symbol line :: 199</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3827,22 +3515,18 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L555: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L214: isolated marker/symbol line :: 90</t>
+          <t>L206: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L409: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 61</t>
+          <t>L406: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3866,22 +3550,18 @@
       <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L559: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L215: isolated marker/symbol line :: 16</t>
+          <t>L207: isolated marker/symbol line :: 80</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L411: isolated marker/symbol line :: 195</t>
+          <t>L407: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 63</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3905,22 +3585,18 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L560: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L216: isolated marker/symbol line :: 7</t>
+          <t>L208: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L463: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..........</t>
+          <t>L408: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3944,22 +3620,18 @@
       <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L217: isolated marker/symbol line :: 0</t>
+          <t>L209: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L465: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2.........</t>
+          <t>L409: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 61</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3983,22 +3655,18 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L562: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L218: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L210: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L467: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3.........</t>
+          <t>L411: isolated marker/symbol line :: 195</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -4022,22 +3690,18 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L219: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L211: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: 44</t>
+          <t>L463: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..........</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -4061,22 +3725,18 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L220: isolated marker/symbol line :: .</t>
+          <t>L212: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 58</t>
+          <t>L465: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2.........</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4100,22 +3760,18 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L221: isolated marker/symbol line :: .</t>
+          <t>L213: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 82</t>
+          <t>L467: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3.........</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4139,22 +3795,18 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A6 BROKEN BAR :: â€¢â€¦</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L222: isolated marker/symbol line :: 8.</t>
+          <t>L214: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L481: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
+          <t>L469: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4178,22 +3830,18 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: #â€¦</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L223: isolated marker/symbol line :: 78</t>
+          <t>L215: isolated marker/symbol line :: 16</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L483: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ...</t>
+          <t>L470: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4217,22 +3865,18 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L582: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L224: isolated marker/symbol line :: 46</t>
+          <t>L216: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L485: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3...'........</t>
+          <t>L472: isolated marker/symbol line :: 82</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4256,22 +3900,18 @@
       <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L225: isolated marker/symbol line :: 21</t>
+          <t>L217: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L487: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4............</t>
+          <t>L481: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 1 ... ... ...</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4295,22 +3935,18 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L226: isolated marker/symbol line :: e</t>
+          <t>L218: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L489: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5 ... ... ...</t>
+          <t>L483: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 2 ... ... ...</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4334,22 +3970,18 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: ,â€¦</t>
-        </is>
-      </c>
+      <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L227: isolated marker/symbol line :: t</t>
+          <t>L219: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L491: isolated marker/symbol line :: 92</t>
+          <t>L485: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 3...'........</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4373,22 +4005,18 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L228: isolated marker/symbol line :: 8</t>
+          <t>L220: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: 95</t>
+          <t>L487: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 4............</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4412,22 +4040,18 @@
       <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>L599: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L229: isolated marker/symbol line :: .</t>
+          <t>L221: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L495: isolated marker/symbol line :: 84</t>
+          <t>L489: symbol-only separator/garbage line | punctuation artifact: repeated periods :: 5 ... ... ...</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4451,22 +4075,18 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>L600: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Â·â€¦</t>
-        </is>
-      </c>
+      <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L230: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L222: isolated marker/symbol line :: 8.</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 44</t>
+          <t>L491: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4490,22 +4110,18 @@
       <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>L608: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦ 1, 551</t>
-        </is>
-      </c>
+      <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L231: isolated marker/symbol line :: .</t>
+          <t>L223: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L499: isolated marker/symbol line :: 61</t>
+          <t>L493: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4529,22 +4145,18 @@
       <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>L611: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
+      <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L232: isolated marker/symbol line :: .</t>
+          <t>L224: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L501: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 73</t>
+          <t>L495: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4568,22 +4180,18 @@
       <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
+      <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L234: isolated marker/symbol line :: .</t>
+          <t>L225: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L503: isolated marker/symbol line :: 51</t>
+          <t>L497: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4607,22 +4215,18 @@
       <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>L624: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRINT BLOUSES.â€” We have just marked and put in stock 24 dozen Print</t>
-        </is>
-      </c>
+      <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L226: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L505: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 29</t>
+          <t>L499: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
@@ -4646,22 +4250,18 @@
       <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: said it's a h-- of a note or a d â€”â€” of</t>
-        </is>
-      </c>
+      <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L227: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L507: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 59</t>
+          <t>L501: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 73</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
@@ -4685,22 +4285,18 @@
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>L858: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L241: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L228: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L509: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 64</t>
+          <t>L503: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
@@ -4724,22 +4320,18 @@
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t>L911: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gentsâ€™Blouses,</t>
-        </is>
-      </c>
+      <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L242: isolated marker/symbol line :: A</t>
+          <t>L229: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L516: symbol-only separator/garbage line :: $2.00</t>
+          <t>L505: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 29</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
@@ -4763,22 +4355,18 @@
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>L923: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+      <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L267: isolated marker/symbol line :: A.</t>
+          <t>L230: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L518: isolated marker/symbol line :: 276</t>
+          <t>L507: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 59</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
@@ -4802,22 +4390,18 @@
       <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>L1022: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
+      <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L278: isolated marker/symbol line :: 5</t>
+          <t>L231: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L520: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...1,551</t>
+          <t>L509: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 64</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
@@ -4847,10 +4431,14 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L320: isolated marker/symbol line :: 0</t>
-        </is>
-      </c>
-      <c r="O88" s="1" t="inlineStr"/>
+          <t>L232: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O88" s="1" t="inlineStr">
+        <is>
+          <t>L516: symbol-only separator/garbage line :: $2.00</t>
+        </is>
+      </c>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr"/>
       <c r="R88" s="1" t="inlineStr"/>
@@ -4878,10 +4466,14 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L321: isolated marker/symbol line :: 4</t>
-        </is>
-      </c>
-      <c r="O89" s="1" t="inlineStr"/>
+          <t>L233: isolated marker/symbol line :: ……</t>
+        </is>
+      </c>
+      <c r="O89" s="1" t="inlineStr">
+        <is>
+          <t>L518: isolated marker/symbol line :: 276</t>
+        </is>
+      </c>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr"/>
       <c r="R89" s="1" t="inlineStr"/>
@@ -4909,10 +4501,14 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L415: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O90" s="1" t="inlineStr"/>
+          <t>L234: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O90" s="1" t="inlineStr">
+        <is>
+          <t>L520: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...1,551</t>
+        </is>
+      </c>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr"/>
       <c r="R90" s="1" t="inlineStr"/>
@@ -4940,10 +4536,14 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L461: isolated marker/symbol line :: 631</t>
-        </is>
-      </c>
-      <c r="O91" s="1" t="inlineStr"/>
+          <t>L235: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O91" s="1" t="inlineStr">
+        <is>
+          <t>L1062: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
+        </is>
+      </c>
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr"/>
       <c r="R91" s="1" t="inlineStr"/>
@@ -4971,7 +4571,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L462: isolated marker/symbol line :: 284</t>
+          <t>L236: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -5002,7 +4602,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L464: isolated marker/symbol line :: 43</t>
+          <t>L241: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -5033,7 +4633,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L465: isolated marker/symbol line :: 57</t>
+          <t>L242: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -5064,7 +4664,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L466: isolated marker/symbol line :: .</t>
+          <t>L245: stray/suspicious non-ASCII glyph(s): U+FF06 FULLWIDTH AMPERSAND | isolated marker/symbol line :: ＆</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -5095,7 +4695,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L267: isolated marker/symbol line :: A.</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5126,7 +4726,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: 36</t>
+          <t>L278: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5157,7 +4757,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 30</t>
+          <t>L320: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5188,7 +4788,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L471: isolated marker/symbol line :: 29</t>
+          <t>L321: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5219,7 +4819,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L472: isolated marker/symbol line :: 8</t>
+          <t>L415: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5250,7 +4850,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L473: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L461: isolated marker/symbol line :: 631</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5281,7 +4881,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L474: isolated marker/symbol line :: *</t>
+          <t>L462: isolated marker/symbol line :: 284</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5312,7 +4912,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L464: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5343,7 +4943,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L465: isolated marker/symbol line :: 57</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5374,7 +4974,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L477: isolated marker/symbol line :: 46</t>
+          <t>L466: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5405,7 +5005,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L478: isolated marker/symbol line :: 12</t>
+          <t>L467: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5436,7 +5036,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L479: isolated marker/symbol line :: #.</t>
+          <t>L468: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5467,7 +5067,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L480: isolated marker/symbol line :: .</t>
+          <t>L469: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5498,7 +5098,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L481: isolated marker/symbol line :: .</t>
+          <t>L470: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5529,7 +5129,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L482: isolated marker/symbol line :: .</t>
+          <t>L471: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5560,7 +5160,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L483: symbol-only separator/garbage line :: 123456</t>
+          <t>L472: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5591,7 +5191,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L484: isolated marker/symbol line :: 56</t>
+          <t>L473: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5622,7 +5222,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L485: isolated marker/symbol line :: 46</t>
+          <t>L474: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5653,7 +5253,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L486: isolated marker/symbol line :: 0</t>
+          <t>L475: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5684,7 +5284,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L487: isolated marker/symbol line :: #:</t>
+          <t>L476: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5715,7 +5315,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L477: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5746,7 +5346,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L489: isolated marker/symbol line :: #</t>
+          <t>L478: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5777,7 +5377,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L490: isolated marker/symbol line :: 34</t>
+          <t>L479: isolated marker/symbol line :: #.</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5808,7 +5408,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L491: isolated marker/symbol line :: 47</t>
+          <t>L480: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5839,7 +5439,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L492: isolated marker/symbol line :: .</t>
+          <t>L481: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5870,7 +5470,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: .</t>
+          <t>L482: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5901,7 +5501,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L483: symbol-only separator/garbage line :: 123456</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5932,7 +5532,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L495: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L484: isolated marker/symbol line :: 56</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5963,7 +5563,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L485: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5994,7 +5594,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L497: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L486: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -6025,7 +5625,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L487: isolated marker/symbol line :: #:</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -6056,7 +5656,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L500: isolated marker/symbol line :: 35</t>
+          <t>L488: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -6087,7 +5687,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L501: isolated marker/symbol line :: 51</t>
+          <t>L489: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6118,7 +5718,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L502: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L490: isolated marker/symbol line :: 34</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6149,7 +5749,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L491: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6180,7 +5780,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L504: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L492: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6211,7 +5811,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L493: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6242,7 +5842,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L494: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6273,7 +5873,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L507: isolated marker/symbol line :: #0</t>
+          <t>L495: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6304,7 +5904,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L508: isolated marker/symbol line :: 250</t>
+          <t>L496: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6335,7 +5935,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L509: isolated marker/symbol line :: 242</t>
+          <t>L497: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6366,7 +5966,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: 67</t>
+          <t>L498: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6397,7 +5997,7 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 07</t>
+          <t>L499: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6428,7 +6028,7 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L513: isolated marker/symbol line :: 67</t>
+          <t>L500: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6459,7 +6059,7 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L515: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L501: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6490,7 +6090,7 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L516: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L502: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6521,7 +6121,7 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L518: isolated marker/symbol line :: Â·</t>
+          <t>L503: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6552,7 +6152,7 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L519: isolated marker/symbol line :: 78</t>
+          <t>L504: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6583,7 +6183,7 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L520: isolated marker/symbol line :: 52</t>
+          <t>L505: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6614,7 +6214,7 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L521: isolated marker/symbol line :: 123</t>
+          <t>L506: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6645,7 +6245,7 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L523: isolated marker/symbol line :: .</t>
+          <t>L507: isolated marker/symbol line :: #0</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6676,7 +6276,7 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L524: isolated marker/symbol line :: 0</t>
+          <t>L508: isolated marker/symbol line :: 250</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6707,7 +6307,7 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L509: isolated marker/symbol line :: 242</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6738,7 +6338,7 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L511: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -6769,7 +6369,7 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L527: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L512: isolated marker/symbol line :: 07</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -6800,7 +6400,7 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L529: isolated marker/symbol line :: 54</t>
+          <t>L513: isolated marker/symbol line :: 67</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -6831,7 +6431,7 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L530: isolated marker/symbol line :: 45</t>
+          <t>L514: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -6862,7 +6462,7 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L531: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L515: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -6893,7 +6493,7 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L532: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L516: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -6924,7 +6524,7 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L533: isolated marker/symbol line :: .</t>
+          <t>L517: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -6955,7 +6555,7 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L518: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -6986,7 +6586,7 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L535: isolated marker/symbol line :: #.</t>
+          <t>L519: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -7017,7 +6617,7 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L536: isolated marker/symbol line :: 199</t>
+          <t>L520: isolated marker/symbol line :: 52</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -7048,7 +6648,7 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L537: isolated marker/symbol line :: 164</t>
+          <t>L521: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -7079,7 +6679,7 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L538: isolated marker/symbol line :: 0</t>
+          <t>L522: isolated marker/symbol line :: .….</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -7110,7 +6710,7 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L540: isolated marker/symbol line :: 63</t>
+          <t>L523: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -7141,7 +6741,7 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L541: isolated marker/symbol line :: 44</t>
+          <t>L524: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -7172,7 +6772,7 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L542: isolated marker/symbol line :: 1</t>
+          <t>L525: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7203,7 +6803,7 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L543: isolated marker/symbol line :: .</t>
+          <t>L526: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7234,7 +6834,7 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L544: isolated marker/symbol line :: 00</t>
+          <t>L527: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr"/>
@@ -7265,7 +6865,7 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L545: isolated marker/symbol line :: H</t>
+          <t>L528: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O166" s="1" t="inlineStr"/>
@@ -7296,7 +6896,7 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L547: isolated marker/symbol line :: .</t>
+          <t>L529: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O167" s="1" t="inlineStr"/>
@@ -7327,7 +6927,7 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L549: isolated marker/symbol line :: .*</t>
+          <t>L530: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="O168" s="1" t="inlineStr"/>
@@ -7358,7 +6958,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L550: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L531: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -7389,7 +6989,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L551: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L532: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -7420,7 +7020,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L552: isolated marker/symbol line :: 71</t>
+          <t>L533: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -7451,7 +7051,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L553: isolated marker/symbol line :: 58</t>
+          <t>L534: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -7482,7 +7082,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L554: isolated marker/symbol line :: 123</t>
+          <t>L535: isolated marker/symbol line :: #.</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -7513,7 +7113,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L555: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L536: isolated marker/symbol line :: 199</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -7544,7 +7144,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L556: isolated marker/symbol line :: 0</t>
+          <t>L537: isolated marker/symbol line :: 164</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -7575,7 +7175,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L557: isolated marker/symbol line :: Â·</t>
+          <t>L538: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -7606,7 +7206,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L558: isolated marker/symbol line :: .</t>
+          <t>L540: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -7637,7 +7237,7 @@
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L559: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L541: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -7668,7 +7268,7 @@
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L560: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L542: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -7699,7 +7299,7 @@
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L543: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -7730,7 +7330,7 @@
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L562: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L544: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -7761,7 +7361,7 @@
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
         <is>
-          <t>L563: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L545: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr"/>
@@ -7792,7 +7392,7 @@
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L546: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr"/>
@@ -7823,7 +7423,7 @@
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: 2</t>
+          <t>L547: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O184" s="1" t="inlineStr"/>
@@ -7854,7 +7454,7 @@
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: 61</t>
+          <t>L548: isolated marker/symbol line :: .…</t>
         </is>
       </c>
       <c r="O185" s="1" t="inlineStr"/>
@@ -7885,7 +7485,7 @@
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
         <is>
-          <t>L567: isolated marker/symbol line :: 82</t>
+          <t>L549: isolated marker/symbol line :: .*</t>
         </is>
       </c>
       <c r="O186" s="1" t="inlineStr"/>
@@ -7916,7 +7516,7 @@
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
         <is>
-          <t>L568: isolated marker/symbol line :: .</t>
+          <t>L550: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O187" s="1" t="inlineStr"/>
@@ -7947,7 +7547,7 @@
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
         <is>
-          <t>L569: isolated marker/symbol line :: .</t>
+          <t>L551: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O188" s="1" t="inlineStr"/>
@@ -7978,7 +7578,7 @@
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
         <is>
-          <t>L570: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L552: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O189" s="1" t="inlineStr"/>
@@ -8009,7 +7609,7 @@
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
         <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L553: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O190" s="1" t="inlineStr"/>
@@ -8040,7 +7640,7 @@
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
         <is>
-          <t>L573: isolated marker/symbol line :: .</t>
+          <t>L554: isolated marker/symbol line :: 123</t>
         </is>
       </c>
       <c r="O191" s="1" t="inlineStr"/>
@@ -8071,7 +7671,7 @@
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
         <is>
-          <t>L574: isolated marker/symbol line :: 195</t>
+          <t>L555: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O192" s="1" t="inlineStr"/>
@@ -8102,7 +7702,7 @@
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
         <is>
-          <t>L575: isolated marker/symbol line :: 184</t>
+          <t>L556: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O193" s="1" t="inlineStr"/>
@@ -8133,7 +7733,7 @@
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: 73</t>
+          <t>L557: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O194" s="1" t="inlineStr"/>
@@ -8164,7 +7764,7 @@
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: 92</t>
+          <t>L558: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O195" s="1" t="inlineStr"/>
@@ -8195,7 +7795,7 @@
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
         <is>
-          <t>L579: isolated marker/symbol line :: .</t>
+          <t>L559: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O196" s="1" t="inlineStr"/>
@@ -8226,7 +7826,7 @@
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
         <is>
-          <t>L581: isolated marker/symbol line :: .</t>
+          <t>L560: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O197" s="1" t="inlineStr"/>
@@ -8257,7 +7857,7 @@
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
         <is>
-          <t>L582: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L561: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O198" s="1" t="inlineStr"/>
@@ -8288,7 +7888,7 @@
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
         <is>
-          <t>L583: isolated marker/symbol line :: 51</t>
+          <t>L562: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O199" s="1" t="inlineStr"/>
@@ -8319,7 +7919,7 @@
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
         <is>
-          <t>L584: isolated marker/symbol line :: 95</t>
+          <t>L563: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O200" s="1" t="inlineStr"/>
@@ -8350,7 +7950,7 @@
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
         <is>
-          <t>L585: isolated marker/symbol line :: 9</t>
+          <t>L564: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O201" s="1" t="inlineStr"/>
@@ -8381,7 +7981,7 @@
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
         <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L565: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O202" s="1" t="inlineStr"/>
@@ -8412,7 +8012,7 @@
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
         <is>
-          <t>L587: isolated marker/symbol line :: .</t>
+          <t>L566: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O203" s="1" t="inlineStr"/>
@@ -8443,7 +8043,7 @@
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
         <is>
-          <t>L588: isolated marker/symbol line :: 29</t>
+          <t>L567: isolated marker/symbol line :: 82</t>
         </is>
       </c>
       <c r="O204" s="1" t="inlineStr"/>
@@ -8474,7 +8074,7 @@
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
         <is>
-          <t>L589: isolated marker/symbol line :: 84</t>
+          <t>L568: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O205" s="1" t="inlineStr"/>
@@ -8505,7 +8105,7 @@
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
         <is>
-          <t>L590: symbol-only separator/garbage line :: 12845</t>
+          <t>L569: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O206" s="1" t="inlineStr"/>
@@ -8536,7 +8136,7 @@
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
         <is>
-          <t>L591: isolated marker/symbol line :: 59</t>
+          <t>L570: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O207" s="1" t="inlineStr"/>
@@ -8567,7 +8167,7 @@
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
         <is>
-          <t>L592: isolated marker/symbol line :: 44</t>
+          <t>L571: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O208" s="1" t="inlineStr"/>
@@ -8598,7 +8198,7 @@
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
         <is>
-          <t>L593: isolated marker/symbol line :: .</t>
+          <t>L572: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •…</t>
         </is>
       </c>
       <c r="O209" s="1" t="inlineStr"/>
@@ -8629,7 +8229,7 @@
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
         <is>
-          <t>L594: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L573: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O210" s="1" t="inlineStr"/>
@@ -8660,7 +8260,7 @@
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
         <is>
-          <t>L596: isolated marker/symbol line :: 64</t>
+          <t>L574: isolated marker/symbol line :: 195</t>
         </is>
       </c>
       <c r="O211" s="1" t="inlineStr"/>
@@ -8691,7 +8291,7 @@
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
         <is>
-          <t>L597: isolated marker/symbol line :: 61</t>
+          <t>L575: isolated marker/symbol line :: 184</t>
         </is>
       </c>
       <c r="O212" s="1" t="inlineStr"/>
@@ -8722,7 +8322,7 @@
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
         <is>
-          <t>L599: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L577: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O213" s="1" t="inlineStr"/>
@@ -8753,7 +8353,7 @@
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
         <is>
-          <t>L601: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L578: isolated marker/symbol line :: 92</t>
         </is>
       </c>
       <c r="O214" s="1" t="inlineStr"/>
@@ -8784,7 +8384,7 @@
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
         <is>
-          <t>L602: isolated marker/symbol line :: .</t>
+          <t>L579: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O215" s="1" t="inlineStr"/>
@@ -8815,7 +8415,7 @@
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
         <is>
-          <t>L603: isolated marker/symbol line :: .</t>
+          <t>L580: isolated marker/symbol line :: #…</t>
         </is>
       </c>
       <c r="O216" s="1" t="inlineStr"/>
@@ -8846,7 +8446,7 @@
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
         <is>
-          <t>L604: isolated marker/symbol line :: 276</t>
+          <t>L581: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O217" s="1" t="inlineStr"/>
@@ -8877,7 +8477,7 @@
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
         <is>
-          <t>L605: isolated marker/symbol line :: 376</t>
+          <t>L582: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O218" s="1" t="inlineStr"/>
@@ -8908,7 +8508,7 @@
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: *</t>
+          <t>L583: isolated marker/symbol line :: 51</t>
         </is>
       </c>
       <c r="O219" s="1" t="inlineStr"/>
@@ -8939,7 +8539,7 @@
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
         <is>
-          <t>L607: isolated marker/symbol line :: R</t>
+          <t>L584: isolated marker/symbol line :: 95</t>
         </is>
       </c>
       <c r="O220" s="1" t="inlineStr"/>
@@ -8970,7 +8570,7 @@
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
         <is>
-          <t>L609: symbol-only separator/garbage line :: 1, 250</t>
+          <t>L585: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O221" s="1" t="inlineStr"/>
@@ -9001,7 +8601,7 @@
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
         <is>
-          <t>L611: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L586: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O222" s="1" t="inlineStr"/>
@@ -9032,7 +8632,7 @@
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
         <is>
-          <t>L613: isolated marker/symbol line :: .</t>
+          <t>L587: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O223" s="1" t="inlineStr"/>
@@ -9063,7 +8663,7 @@
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
         <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L588: isolated marker/symbol line :: 29</t>
         </is>
       </c>
       <c r="O224" s="1" t="inlineStr"/>
@@ -9094,7 +8694,7 @@
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: .</t>
+          <t>L589: isolated marker/symbol line :: 84</t>
         </is>
       </c>
       <c r="O225" s="1" t="inlineStr"/>
@@ -9125,7 +8725,7 @@
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
         <is>
-          <t>L617: symbol-only separator/garbage line :: $2.00</t>
+          <t>L590: symbol-only separator/garbage line :: 12845</t>
         </is>
       </c>
       <c r="O226" s="1" t="inlineStr"/>
@@ -9156,7 +8756,7 @@
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
         <is>
-          <t>L622: isolated marker/symbol line :: '</t>
+          <t>L591: isolated marker/symbol line :: 59</t>
         </is>
       </c>
       <c r="O227" s="1" t="inlineStr"/>
@@ -9187,7 +8787,7 @@
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
         <is>
-          <t>L623: symbol-only separator/garbage line :: $1.75</t>
+          <t>L592: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="O228" s="1" t="inlineStr"/>
@@ -9218,7 +8818,7 @@
       <c r="M229" s="1" t="inlineStr"/>
       <c r="N229" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: 2</t>
+          <t>L593: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O229" s="1" t="inlineStr"/>
@@ -9249,7 +8849,7 @@
       <c r="M230" s="1" t="inlineStr"/>
       <c r="N230" s="1" t="inlineStr">
         <is>
-          <t>L635: symbol-only separator/garbage line :: $2.00</t>
+          <t>L594: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O230" s="1" t="inlineStr"/>
@@ -9280,7 +8880,7 @@
       <c r="M231" s="1" t="inlineStr"/>
       <c r="N231" s="1" t="inlineStr">
         <is>
-          <t>L654: isolated marker/symbol line :: 2</t>
+          <t>L595: isolated marker/symbol line :: ,…</t>
         </is>
       </c>
       <c r="O231" s="1" t="inlineStr"/>
@@ -9311,7 +8911,7 @@
       <c r="M232" s="1" t="inlineStr"/>
       <c r="N232" s="1" t="inlineStr">
         <is>
-          <t>L692: isolated marker/symbol line :: '</t>
+          <t>L596: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O232" s="1" t="inlineStr"/>
@@ -9342,7 +8942,7 @@
       <c r="M233" s="1" t="inlineStr"/>
       <c r="N233" s="1" t="inlineStr">
         <is>
-          <t>L709: isolated marker/symbol line :: 4</t>
+          <t>L597: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O233" s="1" t="inlineStr"/>
@@ -9373,7 +8973,7 @@
       <c r="M234" s="1" t="inlineStr"/>
       <c r="N234" s="1" t="inlineStr">
         <is>
-          <t>L722: isolated marker/symbol line :: I</t>
+          <t>L598: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O234" s="1" t="inlineStr"/>
@@ -9404,7 +9004,7 @@
       <c r="M235" s="1" t="inlineStr"/>
       <c r="N235" s="1" t="inlineStr">
         <is>
-          <t>L858: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L599: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O235" s="1" t="inlineStr"/>
@@ -9435,7 +9035,7 @@
       <c r="M236" s="1" t="inlineStr"/>
       <c r="N236" s="1" t="inlineStr">
         <is>
-          <t>L923: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L600: isolated marker/symbol line :: ·…</t>
         </is>
       </c>
       <c r="O236" s="1" t="inlineStr"/>
@@ -9466,7 +9066,7 @@
       <c r="M237" s="1" t="inlineStr"/>
       <c r="N237" s="1" t="inlineStr">
         <is>
-          <t>L927: isolated marker/symbol line :: 18</t>
+          <t>L601: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O237" s="1" t="inlineStr"/>
@@ -9497,7 +9097,7 @@
       <c r="M238" s="1" t="inlineStr"/>
       <c r="N238" s="1" t="inlineStr">
         <is>
-          <t>L929: isolated marker/symbol line :: 20</t>
+          <t>L602: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O238" s="1" t="inlineStr"/>
@@ -9528,7 +9128,7 @@
       <c r="M239" s="1" t="inlineStr"/>
       <c r="N239" s="1" t="inlineStr">
         <is>
-          <t>L949: symbol-only separator/garbage line :: $5.25</t>
+          <t>L603: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O239" s="1" t="inlineStr"/>
@@ -9559,7 +9159,7 @@
       <c r="M240" s="1" t="inlineStr"/>
       <c r="N240" s="1" t="inlineStr">
         <is>
-          <t>L952: isolated marker/symbol line :: c</t>
+          <t>L604: isolated marker/symbol line :: 276</t>
         </is>
       </c>
       <c r="O240" s="1" t="inlineStr"/>
@@ -9590,7 +9190,7 @@
       <c r="M241" s="1" t="inlineStr"/>
       <c r="N241" s="1" t="inlineStr">
         <is>
-          <t>L969: isolated marker/symbol line :: C</t>
+          <t>L605: isolated marker/symbol line :: 376</t>
         </is>
       </c>
       <c r="O241" s="1" t="inlineStr"/>
@@ -9621,7 +9221,7 @@
       <c r="M242" s="1" t="inlineStr"/>
       <c r="N242" s="1" t="inlineStr">
         <is>
-          <t>L999: symbol-only separator/garbage line :: $1.50.</t>
+          <t>L606: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O242" s="1" t="inlineStr"/>
@@ -9652,7 +9252,7 @@
       <c r="M243" s="1" t="inlineStr"/>
       <c r="N243" s="1" t="inlineStr">
         <is>
-          <t>L1022: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L607: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="O243" s="1" t="inlineStr"/>
@@ -9683,7 +9283,7 @@
       <c r="M244" s="1" t="inlineStr"/>
       <c r="N244" s="1" t="inlineStr">
         <is>
-          <t>L1052: isolated marker/symbol line :: 5</t>
+          <t>L608: symbol-only separator/garbage line :: …… 1, 551</t>
         </is>
       </c>
       <c r="O244" s="1" t="inlineStr"/>
@@ -9698,6 +9298,936 @@
       <c r="X244" s="1" t="inlineStr"/>
       <c r="Y244" s="1" t="inlineStr"/>
     </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr"/>
+      <c r="B245" s="1" t="inlineStr"/>
+      <c r="C245" s="1" t="inlineStr"/>
+      <c r="D245" s="1" t="inlineStr"/>
+      <c r="E245" s="1" t="inlineStr"/>
+      <c r="F245" s="1" t="inlineStr"/>
+      <c r="G245" s="1" t="inlineStr"/>
+      <c r="H245" s="1" t="inlineStr"/>
+      <c r="I245" s="1" t="inlineStr"/>
+      <c r="J245" s="1" t="inlineStr"/>
+      <c r="K245" s="1" t="inlineStr"/>
+      <c r="L245" s="1" t="inlineStr"/>
+      <c r="M245" s="1" t="inlineStr"/>
+      <c r="N245" s="1" t="inlineStr">
+        <is>
+          <t>L609: symbol-only separator/garbage line :: 1, 250</t>
+        </is>
+      </c>
+      <c r="O245" s="1" t="inlineStr"/>
+      <c r="P245" s="1" t="inlineStr"/>
+      <c r="Q245" s="1" t="inlineStr"/>
+      <c r="R245" s="1" t="inlineStr"/>
+      <c r="S245" s="1" t="inlineStr"/>
+      <c r="T245" s="1" t="inlineStr"/>
+      <c r="U245" s="1" t="inlineStr"/>
+      <c r="V245" s="1" t="inlineStr"/>
+      <c r="W245" s="1" t="inlineStr"/>
+      <c r="X245" s="1" t="inlineStr"/>
+      <c r="Y245" s="1" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr"/>
+      <c r="B246" s="1" t="inlineStr"/>
+      <c r="C246" s="1" t="inlineStr"/>
+      <c r="D246" s="1" t="inlineStr"/>
+      <c r="E246" s="1" t="inlineStr"/>
+      <c r="F246" s="1" t="inlineStr"/>
+      <c r="G246" s="1" t="inlineStr"/>
+      <c r="H246" s="1" t="inlineStr"/>
+      <c r="I246" s="1" t="inlineStr"/>
+      <c r="J246" s="1" t="inlineStr"/>
+      <c r="K246" s="1" t="inlineStr"/>
+      <c r="L246" s="1" t="inlineStr"/>
+      <c r="M246" s="1" t="inlineStr"/>
+      <c r="N246" s="1" t="inlineStr">
+        <is>
+          <t>L611: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="O246" s="1" t="inlineStr"/>
+      <c r="P246" s="1" t="inlineStr"/>
+      <c r="Q246" s="1" t="inlineStr"/>
+      <c r="R246" s="1" t="inlineStr"/>
+      <c r="S246" s="1" t="inlineStr"/>
+      <c r="T246" s="1" t="inlineStr"/>
+      <c r="U246" s="1" t="inlineStr"/>
+      <c r="V246" s="1" t="inlineStr"/>
+      <c r="W246" s="1" t="inlineStr"/>
+      <c r="X246" s="1" t="inlineStr"/>
+      <c r="Y246" s="1" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr"/>
+      <c r="B247" s="1" t="inlineStr"/>
+      <c r="C247" s="1" t="inlineStr"/>
+      <c r="D247" s="1" t="inlineStr"/>
+      <c r="E247" s="1" t="inlineStr"/>
+      <c r="F247" s="1" t="inlineStr"/>
+      <c r="G247" s="1" t="inlineStr"/>
+      <c r="H247" s="1" t="inlineStr"/>
+      <c r="I247" s="1" t="inlineStr"/>
+      <c r="J247" s="1" t="inlineStr"/>
+      <c r="K247" s="1" t="inlineStr"/>
+      <c r="L247" s="1" t="inlineStr"/>
+      <c r="M247" s="1" t="inlineStr"/>
+      <c r="N247" s="1" t="inlineStr">
+        <is>
+          <t>L612: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="O247" s="1" t="inlineStr"/>
+      <c r="P247" s="1" t="inlineStr"/>
+      <c r="Q247" s="1" t="inlineStr"/>
+      <c r="R247" s="1" t="inlineStr"/>
+      <c r="S247" s="1" t="inlineStr"/>
+      <c r="T247" s="1" t="inlineStr"/>
+      <c r="U247" s="1" t="inlineStr"/>
+      <c r="V247" s="1" t="inlineStr"/>
+      <c r="W247" s="1" t="inlineStr"/>
+      <c r="X247" s="1" t="inlineStr"/>
+      <c r="Y247" s="1" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr"/>
+      <c r="B248" s="1" t="inlineStr"/>
+      <c r="C248" s="1" t="inlineStr"/>
+      <c r="D248" s="1" t="inlineStr"/>
+      <c r="E248" s="1" t="inlineStr"/>
+      <c r="F248" s="1" t="inlineStr"/>
+      <c r="G248" s="1" t="inlineStr"/>
+      <c r="H248" s="1" t="inlineStr"/>
+      <c r="I248" s="1" t="inlineStr"/>
+      <c r="J248" s="1" t="inlineStr"/>
+      <c r="K248" s="1" t="inlineStr"/>
+      <c r="L248" s="1" t="inlineStr"/>
+      <c r="M248" s="1" t="inlineStr"/>
+      <c r="N248" s="1" t="inlineStr">
+        <is>
+          <t>L613: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O248" s="1" t="inlineStr"/>
+      <c r="P248" s="1" t="inlineStr"/>
+      <c r="Q248" s="1" t="inlineStr"/>
+      <c r="R248" s="1" t="inlineStr"/>
+      <c r="S248" s="1" t="inlineStr"/>
+      <c r="T248" s="1" t="inlineStr"/>
+      <c r="U248" s="1" t="inlineStr"/>
+      <c r="V248" s="1" t="inlineStr"/>
+      <c r="W248" s="1" t="inlineStr"/>
+      <c r="X248" s="1" t="inlineStr"/>
+      <c r="Y248" s="1" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr"/>
+      <c r="B249" s="1" t="inlineStr"/>
+      <c r="C249" s="1" t="inlineStr"/>
+      <c r="D249" s="1" t="inlineStr"/>
+      <c r="E249" s="1" t="inlineStr"/>
+      <c r="F249" s="1" t="inlineStr"/>
+      <c r="G249" s="1" t="inlineStr"/>
+      <c r="H249" s="1" t="inlineStr"/>
+      <c r="I249" s="1" t="inlineStr"/>
+      <c r="J249" s="1" t="inlineStr"/>
+      <c r="K249" s="1" t="inlineStr"/>
+      <c r="L249" s="1" t="inlineStr"/>
+      <c r="M249" s="1" t="inlineStr"/>
+      <c r="N249" s="1" t="inlineStr">
+        <is>
+          <t>L614: isolated marker/symbol line :: …</t>
+        </is>
+      </c>
+      <c r="O249" s="1" t="inlineStr"/>
+      <c r="P249" s="1" t="inlineStr"/>
+      <c r="Q249" s="1" t="inlineStr"/>
+      <c r="R249" s="1" t="inlineStr"/>
+      <c r="S249" s="1" t="inlineStr"/>
+      <c r="T249" s="1" t="inlineStr"/>
+      <c r="U249" s="1" t="inlineStr"/>
+      <c r="V249" s="1" t="inlineStr"/>
+      <c r="W249" s="1" t="inlineStr"/>
+      <c r="X249" s="1" t="inlineStr"/>
+      <c r="Y249" s="1" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr"/>
+      <c r="B250" s="1" t="inlineStr"/>
+      <c r="C250" s="1" t="inlineStr"/>
+      <c r="D250" s="1" t="inlineStr"/>
+      <c r="E250" s="1" t="inlineStr"/>
+      <c r="F250" s="1" t="inlineStr"/>
+      <c r="G250" s="1" t="inlineStr"/>
+      <c r="H250" s="1" t="inlineStr"/>
+      <c r="I250" s="1" t="inlineStr"/>
+      <c r="J250" s="1" t="inlineStr"/>
+      <c r="K250" s="1" t="inlineStr"/>
+      <c r="L250" s="1" t="inlineStr"/>
+      <c r="M250" s="1" t="inlineStr"/>
+      <c r="N250" s="1" t="inlineStr">
+        <is>
+          <t>L615: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O250" s="1" t="inlineStr"/>
+      <c r="P250" s="1" t="inlineStr"/>
+      <c r="Q250" s="1" t="inlineStr"/>
+      <c r="R250" s="1" t="inlineStr"/>
+      <c r="S250" s="1" t="inlineStr"/>
+      <c r="T250" s="1" t="inlineStr"/>
+      <c r="U250" s="1" t="inlineStr"/>
+      <c r="V250" s="1" t="inlineStr"/>
+      <c r="W250" s="1" t="inlineStr"/>
+      <c r="X250" s="1" t="inlineStr"/>
+      <c r="Y250" s="1" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr"/>
+      <c r="B251" s="1" t="inlineStr"/>
+      <c r="C251" s="1" t="inlineStr"/>
+      <c r="D251" s="1" t="inlineStr"/>
+      <c r="E251" s="1" t="inlineStr"/>
+      <c r="F251" s="1" t="inlineStr"/>
+      <c r="G251" s="1" t="inlineStr"/>
+      <c r="H251" s="1" t="inlineStr"/>
+      <c r="I251" s="1" t="inlineStr"/>
+      <c r="J251" s="1" t="inlineStr"/>
+      <c r="K251" s="1" t="inlineStr"/>
+      <c r="L251" s="1" t="inlineStr"/>
+      <c r="M251" s="1" t="inlineStr"/>
+      <c r="N251" s="1" t="inlineStr">
+        <is>
+          <t>L617: symbol-only separator/garbage line :: $2.00</t>
+        </is>
+      </c>
+      <c r="O251" s="1" t="inlineStr"/>
+      <c r="P251" s="1" t="inlineStr"/>
+      <c r="Q251" s="1" t="inlineStr"/>
+      <c r="R251" s="1" t="inlineStr"/>
+      <c r="S251" s="1" t="inlineStr"/>
+      <c r="T251" s="1" t="inlineStr"/>
+      <c r="U251" s="1" t="inlineStr"/>
+      <c r="V251" s="1" t="inlineStr"/>
+      <c r="W251" s="1" t="inlineStr"/>
+      <c r="X251" s="1" t="inlineStr"/>
+      <c r="Y251" s="1" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr"/>
+      <c r="B252" s="1" t="inlineStr"/>
+      <c r="C252" s="1" t="inlineStr"/>
+      <c r="D252" s="1" t="inlineStr"/>
+      <c r="E252" s="1" t="inlineStr"/>
+      <c r="F252" s="1" t="inlineStr"/>
+      <c r="G252" s="1" t="inlineStr"/>
+      <c r="H252" s="1" t="inlineStr"/>
+      <c r="I252" s="1" t="inlineStr"/>
+      <c r="J252" s="1" t="inlineStr"/>
+      <c r="K252" s="1" t="inlineStr"/>
+      <c r="L252" s="1" t="inlineStr"/>
+      <c r="M252" s="1" t="inlineStr"/>
+      <c r="N252" s="1" t="inlineStr">
+        <is>
+          <t>L622: isolated marker/symbol line :: '</t>
+        </is>
+      </c>
+      <c r="O252" s="1" t="inlineStr"/>
+      <c r="P252" s="1" t="inlineStr"/>
+      <c r="Q252" s="1" t="inlineStr"/>
+      <c r="R252" s="1" t="inlineStr"/>
+      <c r="S252" s="1" t="inlineStr"/>
+      <c r="T252" s="1" t="inlineStr"/>
+      <c r="U252" s="1" t="inlineStr"/>
+      <c r="V252" s="1" t="inlineStr"/>
+      <c r="W252" s="1" t="inlineStr"/>
+      <c r="X252" s="1" t="inlineStr"/>
+      <c r="Y252" s="1" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr"/>
+      <c r="B253" s="1" t="inlineStr"/>
+      <c r="C253" s="1" t="inlineStr"/>
+      <c r="D253" s="1" t="inlineStr"/>
+      <c r="E253" s="1" t="inlineStr"/>
+      <c r="F253" s="1" t="inlineStr"/>
+      <c r="G253" s="1" t="inlineStr"/>
+      <c r="H253" s="1" t="inlineStr"/>
+      <c r="I253" s="1" t="inlineStr"/>
+      <c r="J253" s="1" t="inlineStr"/>
+      <c r="K253" s="1" t="inlineStr"/>
+      <c r="L253" s="1" t="inlineStr"/>
+      <c r="M253" s="1" t="inlineStr"/>
+      <c r="N253" s="1" t="inlineStr">
+        <is>
+          <t>L623: symbol-only separator/garbage line :: $1.75</t>
+        </is>
+      </c>
+      <c r="O253" s="1" t="inlineStr"/>
+      <c r="P253" s="1" t="inlineStr"/>
+      <c r="Q253" s="1" t="inlineStr"/>
+      <c r="R253" s="1" t="inlineStr"/>
+      <c r="S253" s="1" t="inlineStr"/>
+      <c r="T253" s="1" t="inlineStr"/>
+      <c r="U253" s="1" t="inlineStr"/>
+      <c r="V253" s="1" t="inlineStr"/>
+      <c r="W253" s="1" t="inlineStr"/>
+      <c r="X253" s="1" t="inlineStr"/>
+      <c r="Y253" s="1" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr"/>
+      <c r="B254" s="1" t="inlineStr"/>
+      <c r="C254" s="1" t="inlineStr"/>
+      <c r="D254" s="1" t="inlineStr"/>
+      <c r="E254" s="1" t="inlineStr"/>
+      <c r="F254" s="1" t="inlineStr"/>
+      <c r="G254" s="1" t="inlineStr"/>
+      <c r="H254" s="1" t="inlineStr"/>
+      <c r="I254" s="1" t="inlineStr"/>
+      <c r="J254" s="1" t="inlineStr"/>
+      <c r="K254" s="1" t="inlineStr"/>
+      <c r="L254" s="1" t="inlineStr"/>
+      <c r="M254" s="1" t="inlineStr"/>
+      <c r="N254" s="1" t="inlineStr">
+        <is>
+          <t>L628: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O254" s="1" t="inlineStr"/>
+      <c r="P254" s="1" t="inlineStr"/>
+      <c r="Q254" s="1" t="inlineStr"/>
+      <c r="R254" s="1" t="inlineStr"/>
+      <c r="S254" s="1" t="inlineStr"/>
+      <c r="T254" s="1" t="inlineStr"/>
+      <c r="U254" s="1" t="inlineStr"/>
+      <c r="V254" s="1" t="inlineStr"/>
+      <c r="W254" s="1" t="inlineStr"/>
+      <c r="X254" s="1" t="inlineStr"/>
+      <c r="Y254" s="1" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr"/>
+      <c r="B255" s="1" t="inlineStr"/>
+      <c r="C255" s="1" t="inlineStr"/>
+      <c r="D255" s="1" t="inlineStr"/>
+      <c r="E255" s="1" t="inlineStr"/>
+      <c r="F255" s="1" t="inlineStr"/>
+      <c r="G255" s="1" t="inlineStr"/>
+      <c r="H255" s="1" t="inlineStr"/>
+      <c r="I255" s="1" t="inlineStr"/>
+      <c r="J255" s="1" t="inlineStr"/>
+      <c r="K255" s="1" t="inlineStr"/>
+      <c r="L255" s="1" t="inlineStr"/>
+      <c r="M255" s="1" t="inlineStr"/>
+      <c r="N255" s="1" t="inlineStr">
+        <is>
+          <t>L629: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
+        </is>
+      </c>
+      <c r="O255" s="1" t="inlineStr"/>
+      <c r="P255" s="1" t="inlineStr"/>
+      <c r="Q255" s="1" t="inlineStr"/>
+      <c r="R255" s="1" t="inlineStr"/>
+      <c r="S255" s="1" t="inlineStr"/>
+      <c r="T255" s="1" t="inlineStr"/>
+      <c r="U255" s="1" t="inlineStr"/>
+      <c r="V255" s="1" t="inlineStr"/>
+      <c r="W255" s="1" t="inlineStr"/>
+      <c r="X255" s="1" t="inlineStr"/>
+      <c r="Y255" s="1" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr"/>
+      <c r="B256" s="1" t="inlineStr"/>
+      <c r="C256" s="1" t="inlineStr"/>
+      <c r="D256" s="1" t="inlineStr"/>
+      <c r="E256" s="1" t="inlineStr"/>
+      <c r="F256" s="1" t="inlineStr"/>
+      <c r="G256" s="1" t="inlineStr"/>
+      <c r="H256" s="1" t="inlineStr"/>
+      <c r="I256" s="1" t="inlineStr"/>
+      <c r="J256" s="1" t="inlineStr"/>
+      <c r="K256" s="1" t="inlineStr"/>
+      <c r="L256" s="1" t="inlineStr"/>
+      <c r="M256" s="1" t="inlineStr"/>
+      <c r="N256" s="1" t="inlineStr">
+        <is>
+          <t>L635: symbol-only separator/garbage line :: $2.00</t>
+        </is>
+      </c>
+      <c r="O256" s="1" t="inlineStr"/>
+      <c r="P256" s="1" t="inlineStr"/>
+      <c r="Q256" s="1" t="inlineStr"/>
+      <c r="R256" s="1" t="inlineStr"/>
+      <c r="S256" s="1" t="inlineStr"/>
+      <c r="T256" s="1" t="inlineStr"/>
+      <c r="U256" s="1" t="inlineStr"/>
+      <c r="V256" s="1" t="inlineStr"/>
+      <c r="W256" s="1" t="inlineStr"/>
+      <c r="X256" s="1" t="inlineStr"/>
+      <c r="Y256" s="1" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr"/>
+      <c r="B257" s="1" t="inlineStr"/>
+      <c r="C257" s="1" t="inlineStr"/>
+      <c r="D257" s="1" t="inlineStr"/>
+      <c r="E257" s="1" t="inlineStr"/>
+      <c r="F257" s="1" t="inlineStr"/>
+      <c r="G257" s="1" t="inlineStr"/>
+      <c r="H257" s="1" t="inlineStr"/>
+      <c r="I257" s="1" t="inlineStr"/>
+      <c r="J257" s="1" t="inlineStr"/>
+      <c r="K257" s="1" t="inlineStr"/>
+      <c r="L257" s="1" t="inlineStr"/>
+      <c r="M257" s="1" t="inlineStr"/>
+      <c r="N257" s="1" t="inlineStr">
+        <is>
+          <t>L638: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="O257" s="1" t="inlineStr"/>
+      <c r="P257" s="1" t="inlineStr"/>
+      <c r="Q257" s="1" t="inlineStr"/>
+      <c r="R257" s="1" t="inlineStr"/>
+      <c r="S257" s="1" t="inlineStr"/>
+      <c r="T257" s="1" t="inlineStr"/>
+      <c r="U257" s="1" t="inlineStr"/>
+      <c r="V257" s="1" t="inlineStr"/>
+      <c r="W257" s="1" t="inlineStr"/>
+      <c r="X257" s="1" t="inlineStr"/>
+      <c r="Y257" s="1" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr"/>
+      <c r="B258" s="1" t="inlineStr"/>
+      <c r="C258" s="1" t="inlineStr"/>
+      <c r="D258" s="1" t="inlineStr"/>
+      <c r="E258" s="1" t="inlineStr"/>
+      <c r="F258" s="1" t="inlineStr"/>
+      <c r="G258" s="1" t="inlineStr"/>
+      <c r="H258" s="1" t="inlineStr"/>
+      <c r="I258" s="1" t="inlineStr"/>
+      <c r="J258" s="1" t="inlineStr"/>
+      <c r="K258" s="1" t="inlineStr"/>
+      <c r="L258" s="1" t="inlineStr"/>
+      <c r="M258" s="1" t="inlineStr"/>
+      <c r="N258" s="1" t="inlineStr">
+        <is>
+          <t>L642: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
+        </is>
+      </c>
+      <c r="O258" s="1" t="inlineStr"/>
+      <c r="P258" s="1" t="inlineStr"/>
+      <c r="Q258" s="1" t="inlineStr"/>
+      <c r="R258" s="1" t="inlineStr"/>
+      <c r="S258" s="1" t="inlineStr"/>
+      <c r="T258" s="1" t="inlineStr"/>
+      <c r="U258" s="1" t="inlineStr"/>
+      <c r="V258" s="1" t="inlineStr"/>
+      <c r="W258" s="1" t="inlineStr"/>
+      <c r="X258" s="1" t="inlineStr"/>
+      <c r="Y258" s="1" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr"/>
+      <c r="B259" s="1" t="inlineStr"/>
+      <c r="C259" s="1" t="inlineStr"/>
+      <c r="D259" s="1" t="inlineStr"/>
+      <c r="E259" s="1" t="inlineStr"/>
+      <c r="F259" s="1" t="inlineStr"/>
+      <c r="G259" s="1" t="inlineStr"/>
+      <c r="H259" s="1" t="inlineStr"/>
+      <c r="I259" s="1" t="inlineStr"/>
+      <c r="J259" s="1" t="inlineStr"/>
+      <c r="K259" s="1" t="inlineStr"/>
+      <c r="L259" s="1" t="inlineStr"/>
+      <c r="M259" s="1" t="inlineStr"/>
+      <c r="N259" s="1" t="inlineStr">
+        <is>
+          <t>L654: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O259" s="1" t="inlineStr"/>
+      <c r="P259" s="1" t="inlineStr"/>
+      <c r="Q259" s="1" t="inlineStr"/>
+      <c r="R259" s="1" t="inlineStr"/>
+      <c r="S259" s="1" t="inlineStr"/>
+      <c r="T259" s="1" t="inlineStr"/>
+      <c r="U259" s="1" t="inlineStr"/>
+      <c r="V259" s="1" t="inlineStr"/>
+      <c r="W259" s="1" t="inlineStr"/>
+      <c r="X259" s="1" t="inlineStr"/>
+      <c r="Y259" s="1" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr"/>
+      <c r="B260" s="1" t="inlineStr"/>
+      <c r="C260" s="1" t="inlineStr"/>
+      <c r="D260" s="1" t="inlineStr"/>
+      <c r="E260" s="1" t="inlineStr"/>
+      <c r="F260" s="1" t="inlineStr"/>
+      <c r="G260" s="1" t="inlineStr"/>
+      <c r="H260" s="1" t="inlineStr"/>
+      <c r="I260" s="1" t="inlineStr"/>
+      <c r="J260" s="1" t="inlineStr"/>
+      <c r="K260" s="1" t="inlineStr"/>
+      <c r="L260" s="1" t="inlineStr"/>
+      <c r="M260" s="1" t="inlineStr"/>
+      <c r="N260" s="1" t="inlineStr">
+        <is>
+          <t>L692: isolated marker/symbol line :: '</t>
+        </is>
+      </c>
+      <c r="O260" s="1" t="inlineStr"/>
+      <c r="P260" s="1" t="inlineStr"/>
+      <c r="Q260" s="1" t="inlineStr"/>
+      <c r="R260" s="1" t="inlineStr"/>
+      <c r="S260" s="1" t="inlineStr"/>
+      <c r="T260" s="1" t="inlineStr"/>
+      <c r="U260" s="1" t="inlineStr"/>
+      <c r="V260" s="1" t="inlineStr"/>
+      <c r="W260" s="1" t="inlineStr"/>
+      <c r="X260" s="1" t="inlineStr"/>
+      <c r="Y260" s="1" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr"/>
+      <c r="B261" s="1" t="inlineStr"/>
+      <c r="C261" s="1" t="inlineStr"/>
+      <c r="D261" s="1" t="inlineStr"/>
+      <c r="E261" s="1" t="inlineStr"/>
+      <c r="F261" s="1" t="inlineStr"/>
+      <c r="G261" s="1" t="inlineStr"/>
+      <c r="H261" s="1" t="inlineStr"/>
+      <c r="I261" s="1" t="inlineStr"/>
+      <c r="J261" s="1" t="inlineStr"/>
+      <c r="K261" s="1" t="inlineStr"/>
+      <c r="L261" s="1" t="inlineStr"/>
+      <c r="M261" s="1" t="inlineStr"/>
+      <c r="N261" s="1" t="inlineStr">
+        <is>
+          <t>L709: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O261" s="1" t="inlineStr"/>
+      <c r="P261" s="1" t="inlineStr"/>
+      <c r="Q261" s="1" t="inlineStr"/>
+      <c r="R261" s="1" t="inlineStr"/>
+      <c r="S261" s="1" t="inlineStr"/>
+      <c r="T261" s="1" t="inlineStr"/>
+      <c r="U261" s="1" t="inlineStr"/>
+      <c r="V261" s="1" t="inlineStr"/>
+      <c r="W261" s="1" t="inlineStr"/>
+      <c r="X261" s="1" t="inlineStr"/>
+      <c r="Y261" s="1" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr"/>
+      <c r="B262" s="1" t="inlineStr"/>
+      <c r="C262" s="1" t="inlineStr"/>
+      <c r="D262" s="1" t="inlineStr"/>
+      <c r="E262" s="1" t="inlineStr"/>
+      <c r="F262" s="1" t="inlineStr"/>
+      <c r="G262" s="1" t="inlineStr"/>
+      <c r="H262" s="1" t="inlineStr"/>
+      <c r="I262" s="1" t="inlineStr"/>
+      <c r="J262" s="1" t="inlineStr"/>
+      <c r="K262" s="1" t="inlineStr"/>
+      <c r="L262" s="1" t="inlineStr"/>
+      <c r="M262" s="1" t="inlineStr"/>
+      <c r="N262" s="1" t="inlineStr">
+        <is>
+          <t>L722: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
+      <c r="O262" s="1" t="inlineStr"/>
+      <c r="P262" s="1" t="inlineStr"/>
+      <c r="Q262" s="1" t="inlineStr"/>
+      <c r="R262" s="1" t="inlineStr"/>
+      <c r="S262" s="1" t="inlineStr"/>
+      <c r="T262" s="1" t="inlineStr"/>
+      <c r="U262" s="1" t="inlineStr"/>
+      <c r="V262" s="1" t="inlineStr"/>
+      <c r="W262" s="1" t="inlineStr"/>
+      <c r="X262" s="1" t="inlineStr"/>
+      <c r="Y262" s="1" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr"/>
+      <c r="B263" s="1" t="inlineStr"/>
+      <c r="C263" s="1" t="inlineStr"/>
+      <c r="D263" s="1" t="inlineStr"/>
+      <c r="E263" s="1" t="inlineStr"/>
+      <c r="F263" s="1" t="inlineStr"/>
+      <c r="G263" s="1" t="inlineStr"/>
+      <c r="H263" s="1" t="inlineStr"/>
+      <c r="I263" s="1" t="inlineStr"/>
+      <c r="J263" s="1" t="inlineStr"/>
+      <c r="K263" s="1" t="inlineStr"/>
+      <c r="L263" s="1" t="inlineStr"/>
+      <c r="M263" s="1" t="inlineStr"/>
+      <c r="N263" s="1" t="inlineStr">
+        <is>
+          <t>L777: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="O263" s="1" t="inlineStr"/>
+      <c r="P263" s="1" t="inlineStr"/>
+      <c r="Q263" s="1" t="inlineStr"/>
+      <c r="R263" s="1" t="inlineStr"/>
+      <c r="S263" s="1" t="inlineStr"/>
+      <c r="T263" s="1" t="inlineStr"/>
+      <c r="U263" s="1" t="inlineStr"/>
+      <c r="V263" s="1" t="inlineStr"/>
+      <c r="W263" s="1" t="inlineStr"/>
+      <c r="X263" s="1" t="inlineStr"/>
+      <c r="Y263" s="1" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr"/>
+      <c r="B264" s="1" t="inlineStr"/>
+      <c r="C264" s="1" t="inlineStr"/>
+      <c r="D264" s="1" t="inlineStr"/>
+      <c r="E264" s="1" t="inlineStr"/>
+      <c r="F264" s="1" t="inlineStr"/>
+      <c r="G264" s="1" t="inlineStr"/>
+      <c r="H264" s="1" t="inlineStr"/>
+      <c r="I264" s="1" t="inlineStr"/>
+      <c r="J264" s="1" t="inlineStr"/>
+      <c r="K264" s="1" t="inlineStr"/>
+      <c r="L264" s="1" t="inlineStr"/>
+      <c r="M264" s="1" t="inlineStr"/>
+      <c r="N264" s="1" t="inlineStr">
+        <is>
+          <t>L858: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O264" s="1" t="inlineStr"/>
+      <c r="P264" s="1" t="inlineStr"/>
+      <c r="Q264" s="1" t="inlineStr"/>
+      <c r="R264" s="1" t="inlineStr"/>
+      <c r="S264" s="1" t="inlineStr"/>
+      <c r="T264" s="1" t="inlineStr"/>
+      <c r="U264" s="1" t="inlineStr"/>
+      <c r="V264" s="1" t="inlineStr"/>
+      <c r="W264" s="1" t="inlineStr"/>
+      <c r="X264" s="1" t="inlineStr"/>
+      <c r="Y264" s="1" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr"/>
+      <c r="B265" s="1" t="inlineStr"/>
+      <c r="C265" s="1" t="inlineStr"/>
+      <c r="D265" s="1" t="inlineStr"/>
+      <c r="E265" s="1" t="inlineStr"/>
+      <c r="F265" s="1" t="inlineStr"/>
+      <c r="G265" s="1" t="inlineStr"/>
+      <c r="H265" s="1" t="inlineStr"/>
+      <c r="I265" s="1" t="inlineStr"/>
+      <c r="J265" s="1" t="inlineStr"/>
+      <c r="K265" s="1" t="inlineStr"/>
+      <c r="L265" s="1" t="inlineStr"/>
+      <c r="M265" s="1" t="inlineStr"/>
+      <c r="N265" s="1" t="inlineStr">
+        <is>
+          <t>L923: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O265" s="1" t="inlineStr"/>
+      <c r="P265" s="1" t="inlineStr"/>
+      <c r="Q265" s="1" t="inlineStr"/>
+      <c r="R265" s="1" t="inlineStr"/>
+      <c r="S265" s="1" t="inlineStr"/>
+      <c r="T265" s="1" t="inlineStr"/>
+      <c r="U265" s="1" t="inlineStr"/>
+      <c r="V265" s="1" t="inlineStr"/>
+      <c r="W265" s="1" t="inlineStr"/>
+      <c r="X265" s="1" t="inlineStr"/>
+      <c r="Y265" s="1" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr"/>
+      <c r="B266" s="1" t="inlineStr"/>
+      <c r="C266" s="1" t="inlineStr"/>
+      <c r="D266" s="1" t="inlineStr"/>
+      <c r="E266" s="1" t="inlineStr"/>
+      <c r="F266" s="1" t="inlineStr"/>
+      <c r="G266" s="1" t="inlineStr"/>
+      <c r="H266" s="1" t="inlineStr"/>
+      <c r="I266" s="1" t="inlineStr"/>
+      <c r="J266" s="1" t="inlineStr"/>
+      <c r="K266" s="1" t="inlineStr"/>
+      <c r="L266" s="1" t="inlineStr"/>
+      <c r="M266" s="1" t="inlineStr"/>
+      <c r="N266" s="1" t="inlineStr">
+        <is>
+          <t>L927: isolated marker/symbol line :: 18</t>
+        </is>
+      </c>
+      <c r="O266" s="1" t="inlineStr"/>
+      <c r="P266" s="1" t="inlineStr"/>
+      <c r="Q266" s="1" t="inlineStr"/>
+      <c r="R266" s="1" t="inlineStr"/>
+      <c r="S266" s="1" t="inlineStr"/>
+      <c r="T266" s="1" t="inlineStr"/>
+      <c r="U266" s="1" t="inlineStr"/>
+      <c r="V266" s="1" t="inlineStr"/>
+      <c r="W266" s="1" t="inlineStr"/>
+      <c r="X266" s="1" t="inlineStr"/>
+      <c r="Y266" s="1" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr"/>
+      <c r="B267" s="1" t="inlineStr"/>
+      <c r="C267" s="1" t="inlineStr"/>
+      <c r="D267" s="1" t="inlineStr"/>
+      <c r="E267" s="1" t="inlineStr"/>
+      <c r="F267" s="1" t="inlineStr"/>
+      <c r="G267" s="1" t="inlineStr"/>
+      <c r="H267" s="1" t="inlineStr"/>
+      <c r="I267" s="1" t="inlineStr"/>
+      <c r="J267" s="1" t="inlineStr"/>
+      <c r="K267" s="1" t="inlineStr"/>
+      <c r="L267" s="1" t="inlineStr"/>
+      <c r="M267" s="1" t="inlineStr"/>
+      <c r="N267" s="1" t="inlineStr">
+        <is>
+          <t>L929: isolated marker/symbol line :: 20</t>
+        </is>
+      </c>
+      <c r="O267" s="1" t="inlineStr"/>
+      <c r="P267" s="1" t="inlineStr"/>
+      <c r="Q267" s="1" t="inlineStr"/>
+      <c r="R267" s="1" t="inlineStr"/>
+      <c r="S267" s="1" t="inlineStr"/>
+      <c r="T267" s="1" t="inlineStr"/>
+      <c r="U267" s="1" t="inlineStr"/>
+      <c r="V267" s="1" t="inlineStr"/>
+      <c r="W267" s="1" t="inlineStr"/>
+      <c r="X267" s="1" t="inlineStr"/>
+      <c r="Y267" s="1" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr"/>
+      <c r="B268" s="1" t="inlineStr"/>
+      <c r="C268" s="1" t="inlineStr"/>
+      <c r="D268" s="1" t="inlineStr"/>
+      <c r="E268" s="1" t="inlineStr"/>
+      <c r="F268" s="1" t="inlineStr"/>
+      <c r="G268" s="1" t="inlineStr"/>
+      <c r="H268" s="1" t="inlineStr"/>
+      <c r="I268" s="1" t="inlineStr"/>
+      <c r="J268" s="1" t="inlineStr"/>
+      <c r="K268" s="1" t="inlineStr"/>
+      <c r="L268" s="1" t="inlineStr"/>
+      <c r="M268" s="1" t="inlineStr"/>
+      <c r="N268" s="1" t="inlineStr">
+        <is>
+          <t>L949: symbol-only separator/garbage line :: $5.25</t>
+        </is>
+      </c>
+      <c r="O268" s="1" t="inlineStr"/>
+      <c r="P268" s="1" t="inlineStr"/>
+      <c r="Q268" s="1" t="inlineStr"/>
+      <c r="R268" s="1" t="inlineStr"/>
+      <c r="S268" s="1" t="inlineStr"/>
+      <c r="T268" s="1" t="inlineStr"/>
+      <c r="U268" s="1" t="inlineStr"/>
+      <c r="V268" s="1" t="inlineStr"/>
+      <c r="W268" s="1" t="inlineStr"/>
+      <c r="X268" s="1" t="inlineStr"/>
+      <c r="Y268" s="1" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr"/>
+      <c r="B269" s="1" t="inlineStr"/>
+      <c r="C269" s="1" t="inlineStr"/>
+      <c r="D269" s="1" t="inlineStr"/>
+      <c r="E269" s="1" t="inlineStr"/>
+      <c r="F269" s="1" t="inlineStr"/>
+      <c r="G269" s="1" t="inlineStr"/>
+      <c r="H269" s="1" t="inlineStr"/>
+      <c r="I269" s="1" t="inlineStr"/>
+      <c r="J269" s="1" t="inlineStr"/>
+      <c r="K269" s="1" t="inlineStr"/>
+      <c r="L269" s="1" t="inlineStr"/>
+      <c r="M269" s="1" t="inlineStr"/>
+      <c r="N269" s="1" t="inlineStr">
+        <is>
+          <t>L952: isolated marker/symbol line :: c</t>
+        </is>
+      </c>
+      <c r="O269" s="1" t="inlineStr"/>
+      <c r="P269" s="1" t="inlineStr"/>
+      <c r="Q269" s="1" t="inlineStr"/>
+      <c r="R269" s="1" t="inlineStr"/>
+      <c r="S269" s="1" t="inlineStr"/>
+      <c r="T269" s="1" t="inlineStr"/>
+      <c r="U269" s="1" t="inlineStr"/>
+      <c r="V269" s="1" t="inlineStr"/>
+      <c r="W269" s="1" t="inlineStr"/>
+      <c r="X269" s="1" t="inlineStr"/>
+      <c r="Y269" s="1" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr"/>
+      <c r="B270" s="1" t="inlineStr"/>
+      <c r="C270" s="1" t="inlineStr"/>
+      <c r="D270" s="1" t="inlineStr"/>
+      <c r="E270" s="1" t="inlineStr"/>
+      <c r="F270" s="1" t="inlineStr"/>
+      <c r="G270" s="1" t="inlineStr"/>
+      <c r="H270" s="1" t="inlineStr"/>
+      <c r="I270" s="1" t="inlineStr"/>
+      <c r="J270" s="1" t="inlineStr"/>
+      <c r="K270" s="1" t="inlineStr"/>
+      <c r="L270" s="1" t="inlineStr"/>
+      <c r="M270" s="1" t="inlineStr"/>
+      <c r="N270" s="1" t="inlineStr">
+        <is>
+          <t>L957: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
+        </is>
+      </c>
+      <c r="O270" s="1" t="inlineStr"/>
+      <c r="P270" s="1" t="inlineStr"/>
+      <c r="Q270" s="1" t="inlineStr"/>
+      <c r="R270" s="1" t="inlineStr"/>
+      <c r="S270" s="1" t="inlineStr"/>
+      <c r="T270" s="1" t="inlineStr"/>
+      <c r="U270" s="1" t="inlineStr"/>
+      <c r="V270" s="1" t="inlineStr"/>
+      <c r="W270" s="1" t="inlineStr"/>
+      <c r="X270" s="1" t="inlineStr"/>
+      <c r="Y270" s="1" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr"/>
+      <c r="B271" s="1" t="inlineStr"/>
+      <c r="C271" s="1" t="inlineStr"/>
+      <c r="D271" s="1" t="inlineStr"/>
+      <c r="E271" s="1" t="inlineStr"/>
+      <c r="F271" s="1" t="inlineStr"/>
+      <c r="G271" s="1" t="inlineStr"/>
+      <c r="H271" s="1" t="inlineStr"/>
+      <c r="I271" s="1" t="inlineStr"/>
+      <c r="J271" s="1" t="inlineStr"/>
+      <c r="K271" s="1" t="inlineStr"/>
+      <c r="L271" s="1" t="inlineStr"/>
+      <c r="M271" s="1" t="inlineStr"/>
+      <c r="N271" s="1" t="inlineStr">
+        <is>
+          <t>L969: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
+      <c r="O271" s="1" t="inlineStr"/>
+      <c r="P271" s="1" t="inlineStr"/>
+      <c r="Q271" s="1" t="inlineStr"/>
+      <c r="R271" s="1" t="inlineStr"/>
+      <c r="S271" s="1" t="inlineStr"/>
+      <c r="T271" s="1" t="inlineStr"/>
+      <c r="U271" s="1" t="inlineStr"/>
+      <c r="V271" s="1" t="inlineStr"/>
+      <c r="W271" s="1" t="inlineStr"/>
+      <c r="X271" s="1" t="inlineStr"/>
+      <c r="Y271" s="1" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr"/>
+      <c r="B272" s="1" t="inlineStr"/>
+      <c r="C272" s="1" t="inlineStr"/>
+      <c r="D272" s="1" t="inlineStr"/>
+      <c r="E272" s="1" t="inlineStr"/>
+      <c r="F272" s="1" t="inlineStr"/>
+      <c r="G272" s="1" t="inlineStr"/>
+      <c r="H272" s="1" t="inlineStr"/>
+      <c r="I272" s="1" t="inlineStr"/>
+      <c r="J272" s="1" t="inlineStr"/>
+      <c r="K272" s="1" t="inlineStr"/>
+      <c r="L272" s="1" t="inlineStr"/>
+      <c r="M272" s="1" t="inlineStr"/>
+      <c r="N272" s="1" t="inlineStr">
+        <is>
+          <t>L999: symbol-only separator/garbage line :: $1.50.</t>
+        </is>
+      </c>
+      <c r="O272" s="1" t="inlineStr"/>
+      <c r="P272" s="1" t="inlineStr"/>
+      <c r="Q272" s="1" t="inlineStr"/>
+      <c r="R272" s="1" t="inlineStr"/>
+      <c r="S272" s="1" t="inlineStr"/>
+      <c r="T272" s="1" t="inlineStr"/>
+      <c r="U272" s="1" t="inlineStr"/>
+      <c r="V272" s="1" t="inlineStr"/>
+      <c r="W272" s="1" t="inlineStr"/>
+      <c r="X272" s="1" t="inlineStr"/>
+      <c r="Y272" s="1" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr"/>
+      <c r="B273" s="1" t="inlineStr"/>
+      <c r="C273" s="1" t="inlineStr"/>
+      <c r="D273" s="1" t="inlineStr"/>
+      <c r="E273" s="1" t="inlineStr"/>
+      <c r="F273" s="1" t="inlineStr"/>
+      <c r="G273" s="1" t="inlineStr"/>
+      <c r="H273" s="1" t="inlineStr"/>
+      <c r="I273" s="1" t="inlineStr"/>
+      <c r="J273" s="1" t="inlineStr"/>
+      <c r="K273" s="1" t="inlineStr"/>
+      <c r="L273" s="1" t="inlineStr"/>
+      <c r="M273" s="1" t="inlineStr"/>
+      <c r="N273" s="1" t="inlineStr">
+        <is>
+          <t>L1022: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="O273" s="1" t="inlineStr"/>
+      <c r="P273" s="1" t="inlineStr"/>
+      <c r="Q273" s="1" t="inlineStr"/>
+      <c r="R273" s="1" t="inlineStr"/>
+      <c r="S273" s="1" t="inlineStr"/>
+      <c r="T273" s="1" t="inlineStr"/>
+      <c r="U273" s="1" t="inlineStr"/>
+      <c r="V273" s="1" t="inlineStr"/>
+      <c r="W273" s="1" t="inlineStr"/>
+      <c r="X273" s="1" t="inlineStr"/>
+      <c r="Y273" s="1" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr"/>
+      <c r="B274" s="1" t="inlineStr"/>
+      <c r="C274" s="1" t="inlineStr"/>
+      <c r="D274" s="1" t="inlineStr"/>
+      <c r="E274" s="1" t="inlineStr"/>
+      <c r="F274" s="1" t="inlineStr"/>
+      <c r="G274" s="1" t="inlineStr"/>
+      <c r="H274" s="1" t="inlineStr"/>
+      <c r="I274" s="1" t="inlineStr"/>
+      <c r="J274" s="1" t="inlineStr"/>
+      <c r="K274" s="1" t="inlineStr"/>
+      <c r="L274" s="1" t="inlineStr"/>
+      <c r="M274" s="1" t="inlineStr"/>
+      <c r="N274" s="1" t="inlineStr">
+        <is>
+          <t>L1052: isolated marker/symbol line :: 5</t>
+        </is>
+      </c>
+      <c r="O274" s="1" t="inlineStr"/>
+      <c r="P274" s="1" t="inlineStr"/>
+      <c r="Q274" s="1" t="inlineStr"/>
+      <c r="R274" s="1" t="inlineStr"/>
+      <c r="S274" s="1" t="inlineStr"/>
+      <c r="T274" s="1" t="inlineStr"/>
+      <c r="U274" s="1" t="inlineStr"/>
+      <c r="V274" s="1" t="inlineStr"/>
+      <c r="W274" s="1" t="inlineStr"/>
+      <c r="X274" s="1" t="inlineStr"/>
+      <c r="Y274" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
